--- a/workspace/03_database/RDBMS.xlsx
+++ b/workspace/03_database/RDBMS.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\bebc25\java-yong\db\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\bebc25\java-yong\workspace\03_database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB33B9E2-9186-47DB-B702-7B90F5D21E77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92C3E949-C96E-4362-B642-3008DE57CE5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="41172" yWindow="4128" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -571,13 +571,13 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
@@ -863,35 +863,36 @@
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="4.58203125" customWidth="1"/>
-    <col min="2" max="2" width="6.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.08203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.08203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.4140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27.58203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.1640625" customWidth="1"/>
-    <col min="8" max="8" width="6.75" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.08203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="24.75" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="21.83203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.25" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="26.25" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23.1640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11" customWidth="1"/>
+    <col min="13" max="13" width="10.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B3" s="34" t="s">
+      <c r="B3" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
+      <c r="C3" s="35"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="35"/>
       <c r="F3" s="18"/>
       <c r="G3" s="18"/>
-      <c r="H3" s="34" t="s">
+      <c r="H3" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="I3" s="34"/>
-      <c r="J3" s="34"/>
-      <c r="K3" s="34"/>
-      <c r="L3" s="34"/>
+      <c r="I3" s="35"/>
+      <c r="J3" s="35"/>
+      <c r="K3" s="35"/>
+      <c r="L3" s="35"/>
       <c r="M3" s="18"/>
     </row>
     <row r="4" spans="2:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
@@ -1068,13 +1069,13 @@
       </c>
     </row>
     <row r="12" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B12" s="34" t="s">
+      <c r="B12" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="34"/>
-      <c r="D12" s="34"/>
-      <c r="E12" s="34"/>
-      <c r="F12" s="34"/>
+      <c r="C12" s="35"/>
+      <c r="D12" s="35"/>
+      <c r="E12" s="35"/>
+      <c r="F12" s="35"/>
       <c r="G12" s="14"/>
     </row>
     <row r="13" spans="2:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
@@ -1123,7 +1124,7 @@
       <c r="F15" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G15" s="36"/>
+      <c r="G15" s="34"/>
     </row>
     <row r="16" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B16" s="4">
@@ -1141,7 +1142,7 @@
       <c r="F16" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G16" s="36"/>
+      <c r="G16" s="34"/>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B17" s="4">
@@ -1159,7 +1160,7 @@
       <c r="F17" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G17" s="36"/>
+      <c r="G17" s="34"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B18" s="4">
@@ -1177,7 +1178,7 @@
       <c r="F18" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G18" s="36"/>
+      <c r="G18" s="34"/>
     </row>
     <row r="19" spans="2:7" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B19" s="6">
@@ -1195,7 +1196,7 @@
       <c r="F19" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="G19" s="36"/>
+      <c r="G19" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -1513,7 +1514,7 @@
       <c r="H13" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="J13" s="35" t="s">
+      <c r="J13" s="36" t="s">
         <v>65</v>
       </c>
       <c r="K13" s="33" t="s">
@@ -1536,7 +1537,7 @@
       <c r="H14" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="J14" s="35"/>
+      <c r="J14" s="36"/>
       <c r="K14" t="s">
         <v>64</v>
       </c>
@@ -1557,7 +1558,7 @@
       <c r="H15" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="J15" s="35"/>
+      <c r="J15" s="36"/>
       <c r="K15" s="33" t="s">
         <v>63</v>
       </c>

--- a/workspace/03_database/RDBMS.xlsx
+++ b/workspace/03_database/RDBMS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\bebc25\java-yong\workspace\03_database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92C3E949-C96E-4362-B642-3008DE57CE5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D749DCCA-83BA-417E-B61A-7C9B6658C8A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="41172" yWindow="4128" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/workspace/03_database/RDBMS.xlsx
+++ b/workspace/03_database/RDBMS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\bebc25\java-yong\workspace\03_database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D749DCCA-83BA-417E-B61A-7C9B6658C8A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFAB9D17-6439-4420-B6C8-27665FA81A2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="41172" yWindow="4128" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/workspace/03_database/RDBMS.xlsx
+++ b/workspace/03_database/RDBMS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\bebc25\java-yong\workspace\03_database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFAB9D17-6439-4420-B6C8-27665FA81A2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2F30BC1-5FE1-4DE0-BF52-DEA508C9D998}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="41172" yWindow="4128" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -862,7 +862,7 @@
   <dimension ref="B3:M19"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="4.58203125" customWidth="1"/>
+    <col min="1" max="1" width="33" customWidth="1"/>
     <col min="2" max="2" width="7.25" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.4140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="21.25" bestFit="1" customWidth="1"/>
